--- a/Flash card content.xlsx
+++ b/Flash card content.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Document\Study\Japanese\G4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291042C6-A6FE-4004-8B54-35FDBCB0180B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBFCF2C-6FD8-4FE6-BA4A-6996CF92F951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24084" yWindow="660" windowWidth="15864" windowHeight="15900" xr2:uid="{D3C602C6-381D-4CFD-8815-B1AF80E66584}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16896" xr2:uid="{D3C602C6-381D-4CFD-8815-B1AF80E66584}"/>
   </bookViews>
   <sheets>
     <sheet name="Verb" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3596" uniqueCount="2298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3965" uniqueCount="2501">
   <si>
     <t>Word</t>
   </si>
@@ -6934,6 +6934,615 @@
   <si>
     <t>基本体</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>た形</t>
+  </si>
+  <si>
+    <t>意志形</t>
+  </si>
+  <si>
+    <t>ば形</t>
+  </si>
+  <si>
+    <t>しよう</t>
+  </si>
+  <si>
+    <t>すれば</t>
+  </si>
+  <si>
+    <t>乗り換えよう</t>
+  </si>
+  <si>
+    <t>乗り換えれば</t>
+  </si>
+  <si>
+    <t>入れよう</t>
+  </si>
+  <si>
+    <t>入れれば</t>
+  </si>
+  <si>
+    <t>決めよう</t>
+  </si>
+  <si>
+    <t>決めれば</t>
+  </si>
+  <si>
+    <t>調べよう</t>
+  </si>
+  <si>
+    <t>調べれば</t>
+  </si>
+  <si>
+    <t>勤めよう</t>
+  </si>
+  <si>
+    <t>勤めれば</t>
+  </si>
+  <si>
+    <t>やめよう</t>
+  </si>
+  <si>
+    <t>やめれば</t>
+  </si>
+  <si>
+    <t>つけよう</t>
+  </si>
+  <si>
+    <t>つければ</t>
+  </si>
+  <si>
+    <t>できよう</t>
+  </si>
+  <si>
+    <t>できれば</t>
+  </si>
+  <si>
+    <t>止めよう</t>
+  </si>
+  <si>
+    <t>止めれば</t>
+  </si>
+  <si>
+    <t>煮よう</t>
+  </si>
+  <si>
+    <t>煮れば</t>
+  </si>
+  <si>
+    <t>のせよう</t>
+  </si>
+  <si>
+    <t>のせれば</t>
+  </si>
+  <si>
+    <t>始めよう</t>
+  </si>
+  <si>
+    <t>始めれば</t>
+  </si>
+  <si>
+    <t>浴びよう</t>
+  </si>
+  <si>
+    <t>浴びれば</t>
+  </si>
+  <si>
+    <t>いよう</t>
+  </si>
+  <si>
+    <t>いれば</t>
+  </si>
+  <si>
+    <t>落ちよう</t>
+  </si>
+  <si>
+    <t>落ちれば</t>
+  </si>
+  <si>
+    <t>捨てよう</t>
+  </si>
+  <si>
+    <t>捨てれば</t>
+  </si>
+  <si>
+    <t>出よう</t>
+  </si>
+  <si>
+    <t>出れば</t>
+  </si>
+  <si>
+    <t>貼り替えよう</t>
+  </si>
+  <si>
+    <t>貼り替えれば</t>
+  </si>
+  <si>
+    <t>腫れよう</t>
+  </si>
+  <si>
+    <t>腫れれば</t>
+  </si>
+  <si>
+    <t>覚えよう</t>
+  </si>
+  <si>
+    <t>覚えれば</t>
+  </si>
+  <si>
+    <t>疲れよう</t>
+  </si>
+  <si>
+    <t>疲れれば</t>
+  </si>
+  <si>
+    <t>開けよう</t>
+  </si>
+  <si>
+    <t>開ければ</t>
+  </si>
+  <si>
+    <t>遅れよう</t>
+  </si>
+  <si>
+    <t>遅れれば</t>
+  </si>
+  <si>
+    <t>教えよう</t>
+  </si>
+  <si>
+    <t>教えれば</t>
+  </si>
+  <si>
+    <t>降りよう</t>
+  </si>
+  <si>
+    <t>降りれば</t>
+  </si>
+  <si>
+    <t>過ぎよう</t>
+  </si>
+  <si>
+    <t>過ぎれば</t>
+  </si>
+  <si>
+    <t>見せよう</t>
+  </si>
+  <si>
+    <t>見せれば</t>
+  </si>
+  <si>
+    <t>借りよう</t>
+  </si>
+  <si>
+    <t>借りれば</t>
+  </si>
+  <si>
+    <t>忘れよう</t>
+  </si>
+  <si>
+    <t>忘れれば</t>
+  </si>
+  <si>
+    <t>乗ろう</t>
+  </si>
+  <si>
+    <t>乗れば</t>
+  </si>
+  <si>
+    <t>遊ぼう</t>
+  </si>
+  <si>
+    <t>遊べば</t>
+  </si>
+  <si>
+    <t>あろう</t>
+  </si>
+  <si>
+    <t>あれば</t>
+  </si>
+  <si>
+    <t>いらっしゃろう</t>
+  </si>
+  <si>
+    <t>いらっしゃれば</t>
+  </si>
+  <si>
+    <t>住もう</t>
+  </si>
+  <si>
+    <t>住めば</t>
+  </si>
+  <si>
+    <t>出そう</t>
+  </si>
+  <si>
+    <t>出せば</t>
+  </si>
+  <si>
+    <t>入ろう</t>
+  </si>
+  <si>
+    <t>入れば</t>
+  </si>
+  <si>
+    <t>聞こう</t>
+  </si>
+  <si>
+    <t>聞けば</t>
+  </si>
+  <si>
+    <t>切ろう</t>
+  </si>
+  <si>
+    <t>切れば</t>
+  </si>
+  <si>
+    <t>咲こう</t>
+  </si>
+  <si>
+    <t>咲けば</t>
+  </si>
+  <si>
+    <t>会おう</t>
+  </si>
+  <si>
+    <t>会えば</t>
+  </si>
+  <si>
+    <t>集まろう</t>
+  </si>
+  <si>
+    <t>集まれば</t>
+  </si>
+  <si>
+    <t>送ろう</t>
+  </si>
+  <si>
+    <t>送れば</t>
+  </si>
+  <si>
+    <t>込もう</t>
+  </si>
+  <si>
+    <t>込めば</t>
+  </si>
+  <si>
+    <t>誘おう</t>
+  </si>
+  <si>
+    <t>誘えば</t>
+  </si>
+  <si>
+    <t>打とう</t>
+  </si>
+  <si>
+    <t>打てば</t>
+  </si>
+  <si>
+    <t>効こう</t>
+  </si>
+  <si>
+    <t>効けば</t>
+  </si>
+  <si>
+    <t>転ぼう</t>
+  </si>
+  <si>
+    <t>転べば</t>
+  </si>
+  <si>
+    <t>立とう</t>
+  </si>
+  <si>
+    <t>立てば</t>
+  </si>
+  <si>
+    <t>塗ろう</t>
+  </si>
+  <si>
+    <t>塗れば</t>
+  </si>
+  <si>
+    <t>取ろう</t>
+  </si>
+  <si>
+    <t>取れば</t>
+  </si>
+  <si>
+    <t>治ろう</t>
+  </si>
+  <si>
+    <t>治れば</t>
+  </si>
+  <si>
+    <t>なろう</t>
+  </si>
+  <si>
+    <t>なれば</t>
+  </si>
+  <si>
+    <t>飲もう</t>
+  </si>
+  <si>
+    <t>飲めば</t>
+  </si>
+  <si>
+    <t>始まろう</t>
+  </si>
+  <si>
+    <t>始まれば</t>
+  </si>
+  <si>
+    <t>冷やそう</t>
+  </si>
+  <si>
+    <t>冷やせば</t>
+  </si>
+  <si>
+    <t>降ろう</t>
+  </si>
+  <si>
+    <t>降れば</t>
+  </si>
+  <si>
+    <t>待とう</t>
+  </si>
+  <si>
+    <t>待てば</t>
+  </si>
+  <si>
+    <t>磨こう</t>
+  </si>
+  <si>
+    <t>磨けば</t>
+  </si>
+  <si>
+    <t>もらおう</t>
+  </si>
+  <si>
+    <t>もらえば</t>
+  </si>
+  <si>
+    <t>休もう</t>
+  </si>
+  <si>
+    <t>休めば</t>
+  </si>
+  <si>
+    <t>選ぼう</t>
+  </si>
+  <si>
+    <t>選べば</t>
+  </si>
+  <si>
+    <t>飼おう</t>
+  </si>
+  <si>
+    <t>飼えば</t>
+  </si>
+  <si>
+    <t>配ろう</t>
+  </si>
+  <si>
+    <t>配れば</t>
+  </si>
+  <si>
+    <t>知ろう</t>
+  </si>
+  <si>
+    <t>知れば</t>
+  </si>
+  <si>
+    <t>習おう</t>
+  </si>
+  <si>
+    <t>習えば</t>
+  </si>
+  <si>
+    <t>働こう</t>
+  </si>
+  <si>
+    <t>働けば</t>
+  </si>
+  <si>
+    <t>弾こう</t>
+  </si>
+  <si>
+    <t>弾けば</t>
+  </si>
+  <si>
+    <t>申し込もう</t>
+  </si>
+  <si>
+    <t>申し込めば</t>
+  </si>
+  <si>
+    <t>申そう</t>
+  </si>
+  <si>
+    <t>申せば</t>
+  </si>
+  <si>
+    <t>終わろう</t>
+  </si>
+  <si>
+    <t>終われば</t>
+  </si>
+  <si>
+    <t>言おう</t>
+  </si>
+  <si>
+    <t>言えば</t>
+  </si>
+  <si>
+    <t>置こう</t>
+  </si>
+  <si>
+    <t>置けば</t>
+  </si>
+  <si>
+    <t>押そう</t>
+  </si>
+  <si>
+    <t>押せば</t>
+  </si>
+  <si>
+    <t>泳ごう</t>
+  </si>
+  <si>
+    <t>泳げば</t>
+  </si>
+  <si>
+    <t>探そう</t>
+  </si>
+  <si>
+    <t>探せば</t>
+  </si>
+  <si>
+    <t>騒ごう</t>
+  </si>
+  <si>
+    <t>騒げば</t>
+  </si>
+  <si>
+    <t>死のう</t>
+  </si>
+  <si>
+    <t>死ねば</t>
+  </si>
+  <si>
+    <t>座ろう</t>
+  </si>
+  <si>
+    <t>座れば</t>
+  </si>
+  <si>
+    <t>使おう</t>
+  </si>
+  <si>
+    <t>使えば</t>
+  </si>
+  <si>
+    <t>作ろう</t>
+  </si>
+  <si>
+    <t>作れば</t>
+  </si>
+  <si>
+    <t>手伝おう</t>
+  </si>
+  <si>
+    <t>手伝えば</t>
+  </si>
+  <si>
+    <t>話そう</t>
+  </si>
+  <si>
+    <t>話せば</t>
+  </si>
+  <si>
+    <t>持とう</t>
+  </si>
+  <si>
+    <t>持てば</t>
+  </si>
+  <si>
+    <t>呼ぼう</t>
+  </si>
+  <si>
+    <t>呼べば</t>
+  </si>
+  <si>
+    <t>歩こう</t>
+  </si>
+  <si>
+    <t>歩けば</t>
+  </si>
+  <si>
+    <t>急ごう</t>
+  </si>
+  <si>
+    <t>急げば</t>
+  </si>
+  <si>
+    <t>歌おう</t>
+  </si>
+  <si>
+    <t>歌えば</t>
+  </si>
+  <si>
+    <t>かかろう</t>
+  </si>
+  <si>
+    <t>かかれば</t>
+  </si>
+  <si>
+    <t>着こう</t>
+  </si>
+  <si>
+    <t>着けば</t>
+  </si>
+  <si>
+    <t>描こう</t>
+  </si>
+  <si>
+    <t>描けば</t>
+  </si>
+  <si>
+    <t>落とそう</t>
+  </si>
+  <si>
+    <t>落とせば</t>
+  </si>
+  <si>
+    <t>買おう</t>
+  </si>
+  <si>
+    <t>買えば</t>
+  </si>
+  <si>
+    <t>返そう</t>
+  </si>
+  <si>
+    <t>返せば</t>
+  </si>
+  <si>
+    <t>貸そう</t>
+  </si>
+  <si>
+    <t>貸せば</t>
+  </si>
+  <si>
+    <t>分かろう</t>
+  </si>
+  <si>
+    <t>分かれば</t>
+  </si>
+  <si>
+    <t>行こう</t>
+  </si>
+  <si>
+    <t>行けば</t>
+  </si>
+  <si>
+    <t>持ってこよう</t>
+  </si>
+  <si>
+    <t>持ってくれば</t>
+  </si>
+  <si>
+    <t>帰ってこよう</t>
+  </si>
+  <si>
+    <t>帰ってくれば</t>
+  </si>
+  <si>
+    <t>持っていこう</t>
+  </si>
+  <si>
+    <t>持っていけば</t>
   </si>
 </sst>
 </file>
@@ -7317,13 +7926,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A7E8461-0983-4726-B91F-1549A0319E70}">
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7346,22 +7956,31 @@
         <v>1582</v>
       </c>
       <c r="H1" t="s">
+        <v>2298</v>
+      </c>
+      <c r="I1" t="s">
+        <v>2299</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2300</v>
+      </c>
+      <c r="K1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>1256</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1367</v>
       </c>
@@ -7383,17 +8002,26 @@
       <c r="G2" t="s">
         <v>1315</v>
       </c>
+      <c r="H2" t="s">
+        <v>1583</v>
+      </c>
       <c r="I2" t="s">
+        <v>2301</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2302</v>
+      </c>
+      <c r="L2" t="s">
         <v>1355</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>1368</v>
       </c>
-      <c r="L2">
+      <c r="O2">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1262</v>
       </c>
@@ -7416,22 +8044,31 @@
         <v>1593</v>
       </c>
       <c r="H3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2303</v>
+      </c>
+      <c r="J3" t="s">
+        <v>2304</v>
+      </c>
+      <c r="K3" t="s">
         <v>1257</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
         <v>1264</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>1265</v>
       </c>
-      <c r="K3" t="s">
+      <c r="N3" t="s">
         <v>1135</v>
       </c>
-      <c r="L3">
+      <c r="O3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1274</v>
       </c>
@@ -7454,22 +8091,31 @@
         <v>1609</v>
       </c>
       <c r="H4" t="s">
+        <v>1606</v>
+      </c>
+      <c r="I4" t="s">
+        <v>2305</v>
+      </c>
+      <c r="J4" t="s">
+        <v>2306</v>
+      </c>
+      <c r="K4" t="s">
         <v>1257</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>1264</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>1276</v>
       </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>13</v>
       </c>
-      <c r="L4">
+      <c r="O4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1277</v>
       </c>
@@ -7492,22 +8138,31 @@
         <v>1613</v>
       </c>
       <c r="H5" t="s">
+        <v>1610</v>
+      </c>
+      <c r="I5" t="s">
+        <v>2307</v>
+      </c>
+      <c r="J5" t="s">
+        <v>2308</v>
+      </c>
+      <c r="K5" t="s">
         <v>1257</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>1264</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>1279</v>
       </c>
-      <c r="K5" t="s">
+      <c r="N5" t="s">
         <v>13</v>
       </c>
-      <c r="L5">
+      <c r="O5">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1280</v>
       </c>
@@ -7530,22 +8185,31 @@
         <v>1617</v>
       </c>
       <c r="H6" t="s">
+        <v>1614</v>
+      </c>
+      <c r="I6" t="s">
+        <v>2309</v>
+      </c>
+      <c r="J6" t="s">
+        <v>2310</v>
+      </c>
+      <c r="K6" t="s">
         <v>1257</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>1264</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>1282</v>
       </c>
-      <c r="K6" t="s">
+      <c r="N6" t="s">
         <v>13</v>
       </c>
-      <c r="L6">
+      <c r="O6">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1289</v>
       </c>
@@ -7568,22 +8232,31 @@
         <v>1629</v>
       </c>
       <c r="H7" t="s">
+        <v>1626</v>
+      </c>
+      <c r="I7" t="s">
+        <v>2311</v>
+      </c>
+      <c r="J7" t="s">
+        <v>2312</v>
+      </c>
+      <c r="K7" t="s">
         <v>1257</v>
       </c>
-      <c r="I7" t="s">
+      <c r="L7" t="s">
         <v>1264</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
         <v>1291</v>
       </c>
-      <c r="K7" t="s">
+      <c r="N7" t="s">
         <v>13</v>
       </c>
-      <c r="L7">
+      <c r="O7">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1299</v>
       </c>
@@ -7606,22 +8279,31 @@
         <v>1640</v>
       </c>
       <c r="H8" t="s">
+        <v>1637</v>
+      </c>
+      <c r="I8" t="s">
+        <v>2313</v>
+      </c>
+      <c r="J8" t="s">
+        <v>2314</v>
+      </c>
+      <c r="K8" t="s">
         <v>1257</v>
       </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
         <v>1264</v>
       </c>
-      <c r="J8" t="s">
+      <c r="M8" t="s">
         <v>1300</v>
       </c>
-      <c r="K8" t="s">
+      <c r="N8" t="s">
         <v>13</v>
       </c>
-      <c r="L8">
+      <c r="O8">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1311</v>
       </c>
@@ -7644,22 +8326,31 @@
         <v>1656</v>
       </c>
       <c r="H9" t="s">
+        <v>1653</v>
+      </c>
+      <c r="I9" t="s">
+        <v>2315</v>
+      </c>
+      <c r="J9" t="s">
+        <v>2316</v>
+      </c>
+      <c r="K9" t="s">
         <v>1257</v>
       </c>
-      <c r="I9" t="s">
+      <c r="L9" t="s">
         <v>1264</v>
       </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>1313</v>
       </c>
-      <c r="K9" t="s">
+      <c r="N9" t="s">
         <v>13</v>
       </c>
-      <c r="L9">
+      <c r="O9">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1314</v>
       </c>
@@ -7682,22 +8373,31 @@
         <v>1315</v>
       </c>
       <c r="H10" t="s">
+        <v>1657</v>
+      </c>
+      <c r="I10" t="s">
+        <v>2317</v>
+      </c>
+      <c r="J10" t="s">
+        <v>2318</v>
+      </c>
+      <c r="K10" t="s">
         <v>1257</v>
       </c>
-      <c r="I10" t="s">
+      <c r="L10" t="s">
         <v>1264</v>
       </c>
-      <c r="J10" t="s">
+      <c r="M10" t="s">
         <v>1316</v>
       </c>
-      <c r="K10" t="s">
+      <c r="N10" t="s">
         <v>13</v>
       </c>
-      <c r="L10">
+      <c r="O10">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1317</v>
       </c>
@@ -7720,22 +8420,31 @@
         <v>1663</v>
       </c>
       <c r="H11" t="s">
+        <v>1660</v>
+      </c>
+      <c r="I11" t="s">
+        <v>2319</v>
+      </c>
+      <c r="J11" t="s">
+        <v>2320</v>
+      </c>
+      <c r="K11" t="s">
         <v>1257</v>
       </c>
-      <c r="I11" t="s">
+      <c r="L11" t="s">
         <v>1264</v>
       </c>
-      <c r="J11" t="s">
+      <c r="M11" t="s">
         <v>1319</v>
       </c>
-      <c r="K11" t="s">
+      <c r="N11" t="s">
         <v>13</v>
       </c>
-      <c r="L11">
+      <c r="O11">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1320</v>
       </c>
@@ -7758,22 +8467,31 @@
         <v>1667</v>
       </c>
       <c r="H12" t="s">
+        <v>1664</v>
+      </c>
+      <c r="I12" t="s">
+        <v>2321</v>
+      </c>
+      <c r="J12" t="s">
+        <v>2322</v>
+      </c>
+      <c r="K12" t="s">
         <v>1257</v>
       </c>
-      <c r="I12" t="s">
+      <c r="L12" t="s">
         <v>1264</v>
       </c>
-      <c r="J12" t="s">
+      <c r="M12" t="s">
         <v>1322</v>
       </c>
-      <c r="K12" t="s">
+      <c r="N12" t="s">
         <v>13</v>
       </c>
-      <c r="L12">
+      <c r="O12">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1323</v>
       </c>
@@ -7796,22 +8514,31 @@
         <v>1671</v>
       </c>
       <c r="H13" t="s">
+        <v>1668</v>
+      </c>
+      <c r="I13" t="s">
+        <v>2323</v>
+      </c>
+      <c r="J13" t="s">
+        <v>2324</v>
+      </c>
+      <c r="K13" t="s">
         <v>1257</v>
       </c>
-      <c r="I13" t="s">
+      <c r="L13" t="s">
         <v>1264</v>
       </c>
-      <c r="J13" t="s">
+      <c r="M13" t="s">
         <v>1324</v>
       </c>
-      <c r="K13" t="s">
+      <c r="N13" t="s">
         <v>13</v>
       </c>
-      <c r="L13">
+      <c r="O13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1325</v>
       </c>
@@ -7834,22 +8561,31 @@
         <v>1675</v>
       </c>
       <c r="H14" t="s">
+        <v>1672</v>
+      </c>
+      <c r="I14" t="s">
+        <v>2325</v>
+      </c>
+      <c r="J14" t="s">
+        <v>2326</v>
+      </c>
+      <c r="K14" t="s">
         <v>1257</v>
       </c>
-      <c r="I14" t="s">
+      <c r="L14" t="s">
         <v>1264</v>
       </c>
-      <c r="J14" t="s">
+      <c r="M14" t="s">
         <v>1327</v>
       </c>
-      <c r="K14" t="s">
+      <c r="N14" t="s">
         <v>13</v>
       </c>
-      <c r="L14">
+      <c r="O14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1346</v>
       </c>
@@ -7871,17 +8607,26 @@
       <c r="G15" t="s">
         <v>1703</v>
       </c>
+      <c r="H15" t="s">
+        <v>1700</v>
+      </c>
       <c r="I15" t="s">
+        <v>2327</v>
+      </c>
+      <c r="J15" t="s">
+        <v>2328</v>
+      </c>
+      <c r="L15" t="s">
         <v>1264</v>
       </c>
-      <c r="J15" t="s">
+      <c r="M15" t="s">
         <v>1348</v>
       </c>
-      <c r="L15">
+      <c r="O15">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1350</v>
       </c>
@@ -7903,17 +8648,26 @@
       <c r="G16" t="s">
         <v>1601</v>
       </c>
+      <c r="H16" t="s">
+        <v>1704</v>
+      </c>
       <c r="I16" t="s">
+        <v>2329</v>
+      </c>
+      <c r="J16" t="s">
+        <v>2330</v>
+      </c>
+      <c r="L16" t="s">
         <v>1264</v>
       </c>
-      <c r="J16" t="s">
+      <c r="M16" t="s">
         <v>1351</v>
       </c>
-      <c r="L16">
+      <c r="O16">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1356</v>
       </c>
@@ -7935,17 +8689,26 @@
       <c r="G17" t="s">
         <v>1356</v>
       </c>
+      <c r="H17" t="s">
+        <v>1711</v>
+      </c>
       <c r="I17" t="s">
+        <v>2331</v>
+      </c>
+      <c r="J17" t="s">
+        <v>2332</v>
+      </c>
+      <c r="L17" t="s">
         <v>1264</v>
       </c>
-      <c r="J17" t="s">
+      <c r="M17" t="s">
         <v>1358</v>
       </c>
-      <c r="L17">
+      <c r="O17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1364</v>
       </c>
@@ -7967,17 +8730,26 @@
       <c r="G18" t="s">
         <v>1725</v>
       </c>
+      <c r="H18" t="s">
+        <v>1722</v>
+      </c>
       <c r="I18" t="s">
+        <v>2333</v>
+      </c>
+      <c r="J18" t="s">
+        <v>2334</v>
+      </c>
+      <c r="L18" t="s">
         <v>1264</v>
       </c>
-      <c r="J18" t="s">
+      <c r="M18" t="s">
         <v>1366</v>
       </c>
-      <c r="L18">
+      <c r="O18">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1377</v>
       </c>
@@ -7999,17 +8771,26 @@
       <c r="G19" t="s">
         <v>1737</v>
       </c>
+      <c r="H19" t="s">
+        <v>1734</v>
+      </c>
       <c r="I19" t="s">
+        <v>2335</v>
+      </c>
+      <c r="J19" t="s">
+        <v>2336</v>
+      </c>
+      <c r="L19" t="s">
         <v>1264</v>
       </c>
-      <c r="J19" t="s">
+      <c r="M19" t="s">
         <v>1379</v>
       </c>
-      <c r="L19">
+      <c r="O19">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1393</v>
       </c>
@@ -8031,17 +8812,26 @@
       <c r="G20" t="s">
         <v>1769</v>
       </c>
+      <c r="H20" t="s">
+        <v>1766</v>
+      </c>
       <c r="I20" t="s">
+        <v>2337</v>
+      </c>
+      <c r="J20" t="s">
+        <v>2338</v>
+      </c>
+      <c r="L20" t="s">
         <v>1264</v>
       </c>
-      <c r="J20" t="s">
+      <c r="M20" t="s">
         <v>1395</v>
       </c>
-      <c r="L20">
+      <c r="O20">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1396</v>
       </c>
@@ -8063,17 +8853,26 @@
       <c r="G21" t="s">
         <v>1773</v>
       </c>
+      <c r="H21" t="s">
+        <v>1770</v>
+      </c>
       <c r="I21" t="s">
+        <v>2339</v>
+      </c>
+      <c r="J21" t="s">
+        <v>2340</v>
+      </c>
+      <c r="L21" t="s">
         <v>1264</v>
       </c>
-      <c r="J21" t="s">
+      <c r="M21" t="s">
         <v>1398</v>
       </c>
-      <c r="L21">
+      <c r="O21">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1422</v>
       </c>
@@ -8095,17 +8894,26 @@
       <c r="G22" t="s">
         <v>1809</v>
       </c>
+      <c r="H22" t="s">
+        <v>1806</v>
+      </c>
       <c r="I22" t="s">
+        <v>2341</v>
+      </c>
+      <c r="J22" t="s">
+        <v>2342</v>
+      </c>
+      <c r="L22" t="s">
         <v>1264</v>
       </c>
-      <c r="J22" t="s">
+      <c r="M22" t="s">
         <v>1424</v>
       </c>
-      <c r="L22">
+      <c r="O22">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1315</v>
       </c>
@@ -8127,17 +8935,26 @@
       <c r="G23" t="s">
         <v>1315</v>
       </c>
+      <c r="H23" t="s">
+        <v>1657</v>
+      </c>
       <c r="I23" t="s">
+        <v>2317</v>
+      </c>
+      <c r="J23" t="s">
+        <v>2318</v>
+      </c>
+      <c r="L23" t="s">
         <v>1264</v>
       </c>
-      <c r="J23" t="s">
+      <c r="M23" t="s">
         <v>1434</v>
       </c>
-      <c r="L23">
+      <c r="O23">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1377</v>
       </c>
@@ -8159,17 +8976,26 @@
       <c r="G24" t="s">
         <v>1737</v>
       </c>
+      <c r="H24" t="s">
+        <v>1734</v>
+      </c>
       <c r="I24" t="s">
+        <v>2335</v>
+      </c>
+      <c r="J24" t="s">
+        <v>2336</v>
+      </c>
+      <c r="L24" t="s">
         <v>1264</v>
       </c>
-      <c r="J24" t="s">
+      <c r="M24" t="s">
         <v>1454</v>
       </c>
-      <c r="L24">
+      <c r="O24">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1462</v>
       </c>
@@ -8191,17 +9017,26 @@
       <c r="G25" t="s">
         <v>1761</v>
       </c>
+      <c r="H25" t="s">
+        <v>1758</v>
+      </c>
       <c r="I25" t="s">
+        <v>2343</v>
+      </c>
+      <c r="J25" t="s">
+        <v>2344</v>
+      </c>
+      <c r="L25" t="s">
         <v>1264</v>
       </c>
-      <c r="J25" t="s">
+      <c r="M25" t="s">
         <v>1464</v>
       </c>
-      <c r="L25">
+      <c r="O25">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1465</v>
       </c>
@@ -8223,17 +9058,26 @@
       <c r="G26" t="s">
         <v>1845</v>
       </c>
+      <c r="H26" t="s">
+        <v>1842</v>
+      </c>
       <c r="I26" t="s">
+        <v>2345</v>
+      </c>
+      <c r="J26" t="s">
+        <v>2346</v>
+      </c>
+      <c r="L26" t="s">
         <v>1264</v>
       </c>
-      <c r="J26" t="s">
+      <c r="M26" t="s">
         <v>1467</v>
       </c>
-      <c r="L26">
+      <c r="O26">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1471</v>
       </c>
@@ -8255,17 +9099,26 @@
       <c r="G27" t="s">
         <v>1609</v>
       </c>
+      <c r="H27" t="s">
+        <v>1606</v>
+      </c>
       <c r="I27" t="s">
+        <v>2305</v>
+      </c>
+      <c r="J27" t="s">
+        <v>2306</v>
+      </c>
+      <c r="L27" t="s">
         <v>1264</v>
       </c>
-      <c r="J27" t="s">
+      <c r="M27" t="s">
         <v>1472</v>
       </c>
-      <c r="L27">
+      <c r="O27">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1476</v>
       </c>
@@ -8287,17 +9140,26 @@
       <c r="G28" t="s">
         <v>1857</v>
       </c>
+      <c r="H28" t="s">
+        <v>1854</v>
+      </c>
       <c r="I28" t="s">
+        <v>2347</v>
+      </c>
+      <c r="J28" t="s">
+        <v>2348</v>
+      </c>
+      <c r="L28" t="s">
         <v>1264</v>
       </c>
-      <c r="J28" t="s">
+      <c r="M28" t="s">
         <v>1478</v>
       </c>
-      <c r="L28">
+      <c r="O28">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1479</v>
       </c>
@@ -8319,17 +9181,26 @@
       <c r="G29" t="s">
         <v>1861</v>
       </c>
+      <c r="H29" t="s">
+        <v>1858</v>
+      </c>
       <c r="I29" t="s">
+        <v>2349</v>
+      </c>
+      <c r="J29" t="s">
+        <v>2350</v>
+      </c>
+      <c r="L29" t="s">
         <v>1264</v>
       </c>
-      <c r="J29" t="s">
+      <c r="M29" t="s">
         <v>1481</v>
       </c>
-      <c r="L29">
+      <c r="O29">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1537</v>
       </c>
@@ -8351,17 +9222,26 @@
       <c r="G30" t="s">
         <v>1933</v>
       </c>
+      <c r="H30" t="s">
+        <v>1930</v>
+      </c>
       <c r="I30" t="s">
+        <v>2351</v>
+      </c>
+      <c r="J30" t="s">
+        <v>2352</v>
+      </c>
+      <c r="L30" t="s">
         <v>1264</v>
       </c>
-      <c r="J30" t="s">
+      <c r="M30" t="s">
         <v>1539</v>
       </c>
-      <c r="L30">
+      <c r="O30">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1545</v>
       </c>
@@ -8383,17 +9263,26 @@
       <c r="G31" t="s">
         <v>1737</v>
       </c>
+      <c r="H31" t="s">
+        <v>1734</v>
+      </c>
       <c r="I31" t="s">
+        <v>2335</v>
+      </c>
+      <c r="J31" t="s">
+        <v>2336</v>
+      </c>
+      <c r="L31" t="s">
         <v>1264</v>
       </c>
-      <c r="J31" t="s">
+      <c r="M31" t="s">
         <v>1546</v>
       </c>
-      <c r="L31">
+      <c r="O31">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1547</v>
       </c>
@@ -8415,17 +9304,26 @@
       <c r="G32" t="s">
         <v>1945</v>
       </c>
+      <c r="H32" t="s">
+        <v>1942</v>
+      </c>
       <c r="I32" t="s">
+        <v>2353</v>
+      </c>
+      <c r="J32" t="s">
+        <v>2354</v>
+      </c>
+      <c r="L32" t="s">
         <v>1264</v>
       </c>
-      <c r="J32" t="s">
+      <c r="M32" t="s">
         <v>1549</v>
       </c>
-      <c r="L32">
+      <c r="O32">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1550</v>
       </c>
@@ -8447,17 +9345,26 @@
       <c r="G33" t="s">
         <v>1949</v>
       </c>
+      <c r="H33" t="s">
+        <v>1946</v>
+      </c>
       <c r="I33" t="s">
+        <v>2355</v>
+      </c>
+      <c r="J33" t="s">
+        <v>2356</v>
+      </c>
+      <c r="L33" t="s">
         <v>1264</v>
       </c>
-      <c r="J33" t="s">
+      <c r="M33" t="s">
         <v>1552</v>
       </c>
-      <c r="L33">
+      <c r="O33">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1350</v>
       </c>
@@ -8479,17 +9386,26 @@
       <c r="G34" t="s">
         <v>1601</v>
       </c>
+      <c r="H34" t="s">
+        <v>1704</v>
+      </c>
       <c r="I34" t="s">
+        <v>2329</v>
+      </c>
+      <c r="J34" t="s">
+        <v>2330</v>
+      </c>
+      <c r="L34" t="s">
         <v>1264</v>
       </c>
-      <c r="J34" t="s">
+      <c r="M34" t="s">
         <v>1554</v>
       </c>
-      <c r="L34">
+      <c r="O34">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>1569</v>
       </c>
@@ -8511,17 +9427,26 @@
       <c r="G35" t="s">
         <v>1973</v>
       </c>
+      <c r="H35" t="s">
+        <v>1970</v>
+      </c>
       <c r="I35" t="s">
+        <v>2357</v>
+      </c>
+      <c r="J35" t="s">
+        <v>2358</v>
+      </c>
+      <c r="L35" t="s">
         <v>1264</v>
       </c>
-      <c r="J35" t="s">
+      <c r="M35" t="s">
         <v>1571</v>
       </c>
-      <c r="L35">
+      <c r="O35">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>1575</v>
       </c>
@@ -8543,17 +9468,26 @@
       <c r="G36" t="s">
         <v>1765</v>
       </c>
+      <c r="H36" t="s">
+        <v>1762</v>
+      </c>
       <c r="I36" t="s">
+        <v>2359</v>
+      </c>
+      <c r="J36" t="s">
+        <v>2360</v>
+      </c>
+      <c r="L36" t="s">
         <v>1264</v>
       </c>
-      <c r="J36" t="s">
+      <c r="M36" t="s">
         <v>1577</v>
       </c>
-      <c r="L36">
+      <c r="O36">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1258</v>
       </c>
@@ -8576,22 +9510,31 @@
         <v>1589</v>
       </c>
       <c r="H37" t="s">
+        <v>1586</v>
+      </c>
+      <c r="I37" t="s">
+        <v>2361</v>
+      </c>
+      <c r="J37" t="s">
+        <v>2362</v>
+      </c>
+      <c r="K37" t="s">
         <v>1257</v>
       </c>
-      <c r="I37" t="s">
+      <c r="L37" t="s">
         <v>1260</v>
       </c>
-      <c r="J37" t="s">
+      <c r="M37" t="s">
         <v>1261</v>
       </c>
-      <c r="K37" t="s">
+      <c r="N37" t="s">
         <v>13</v>
       </c>
-      <c r="L37">
+      <c r="O37">
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1266</v>
       </c>
@@ -8614,22 +9557,31 @@
         <v>1597</v>
       </c>
       <c r="H38" t="s">
+        <v>1594</v>
+      </c>
+      <c r="I38" t="s">
+        <v>2363</v>
+      </c>
+      <c r="J38" t="s">
+        <v>2364</v>
+      </c>
+      <c r="K38" t="s">
         <v>1257</v>
       </c>
-      <c r="I38" t="s">
+      <c r="L38" t="s">
         <v>1260</v>
       </c>
-      <c r="J38" t="s">
+      <c r="M38" t="s">
         <v>1268</v>
       </c>
-      <c r="K38" t="s">
+      <c r="N38" t="s">
         <v>13</v>
       </c>
-      <c r="L38">
+      <c r="O38">
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1269</v>
       </c>
@@ -8652,22 +9604,31 @@
         <v>1601</v>
       </c>
       <c r="H39" t="s">
+        <v>1598</v>
+      </c>
+      <c r="I39" t="s">
+        <v>2365</v>
+      </c>
+      <c r="J39" t="s">
+        <v>2366</v>
+      </c>
+      <c r="K39" t="s">
         <v>1257</v>
       </c>
-      <c r="I39" t="s">
+      <c r="L39" t="s">
         <v>1260</v>
       </c>
-      <c r="J39" t="s">
+      <c r="M39" t="s">
         <v>1271</v>
       </c>
-      <c r="K39" t="s">
+      <c r="N39" t="s">
         <v>13</v>
       </c>
-      <c r="L39">
+      <c r="O39">
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>1272</v>
       </c>
@@ -8690,22 +9651,31 @@
         <v>1605</v>
       </c>
       <c r="H40" t="s">
+        <v>1602</v>
+      </c>
+      <c r="I40" t="s">
+        <v>2367</v>
+      </c>
+      <c r="J40" t="s">
+        <v>2368</v>
+      </c>
+      <c r="K40" t="s">
         <v>1257</v>
       </c>
-      <c r="I40" t="s">
+      <c r="L40" t="s">
         <v>1260</v>
       </c>
-      <c r="J40" t="s">
+      <c r="M40" t="s">
         <v>1273</v>
       </c>
-      <c r="K40" t="s">
+      <c r="N40" t="s">
         <v>13</v>
       </c>
-      <c r="L40">
+      <c r="O40">
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>1283</v>
       </c>
@@ -8728,22 +9698,31 @@
         <v>1621</v>
       </c>
       <c r="H41" t="s">
+        <v>1618</v>
+      </c>
+      <c r="I41" t="s">
+        <v>2369</v>
+      </c>
+      <c r="J41" t="s">
+        <v>2370</v>
+      </c>
+      <c r="K41" t="s">
         <v>1257</v>
       </c>
-      <c r="I41" t="s">
+      <c r="L41" t="s">
         <v>1260</v>
       </c>
-      <c r="J41" t="s">
+      <c r="M41" t="s">
         <v>1285</v>
       </c>
-      <c r="K41" t="s">
+      <c r="N41" t="s">
         <v>13</v>
       </c>
-      <c r="L41">
+      <c r="O41">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>1286</v>
       </c>
@@ -8766,22 +9745,31 @@
         <v>1625</v>
       </c>
       <c r="H42" t="s">
+        <v>1622</v>
+      </c>
+      <c r="I42" t="s">
+        <v>2371</v>
+      </c>
+      <c r="J42" t="s">
+        <v>2372</v>
+      </c>
+      <c r="K42" t="s">
         <v>1257</v>
       </c>
-      <c r="I42" t="s">
+      <c r="L42" t="s">
         <v>1260</v>
       </c>
-      <c r="J42" t="s">
+      <c r="M42" t="s">
         <v>1288</v>
       </c>
-      <c r="K42" t="s">
+      <c r="N42" t="s">
         <v>13</v>
       </c>
-      <c r="L42">
+      <c r="O42">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>1296</v>
       </c>
@@ -8804,22 +9792,31 @@
         <v>1471</v>
       </c>
       <c r="H43" t="s">
+        <v>1634</v>
+      </c>
+      <c r="I43" t="s">
+        <v>2373</v>
+      </c>
+      <c r="J43" t="s">
+        <v>2374</v>
+      </c>
+      <c r="K43" t="s">
         <v>1257</v>
       </c>
-      <c r="I43" t="s">
+      <c r="L43" t="s">
         <v>1260</v>
       </c>
-      <c r="J43" t="s">
+      <c r="M43" t="s">
         <v>1298</v>
       </c>
-      <c r="K43" t="s">
+      <c r="N43" t="s">
         <v>13</v>
       </c>
-      <c r="L43">
+      <c r="O43">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>1301</v>
       </c>
@@ -8842,22 +9839,31 @@
         <v>1644</v>
       </c>
       <c r="H44" t="s">
+        <v>1641</v>
+      </c>
+      <c r="I44" t="s">
+        <v>2375</v>
+      </c>
+      <c r="J44" t="s">
+        <v>2376</v>
+      </c>
+      <c r="K44" t="s">
         <v>1257</v>
       </c>
-      <c r="I44" t="s">
+      <c r="L44" t="s">
         <v>1260</v>
       </c>
-      <c r="J44" t="s">
+      <c r="M44" t="s">
         <v>1303</v>
       </c>
-      <c r="K44" t="s">
+      <c r="N44" t="s">
         <v>13</v>
       </c>
-      <c r="L44">
+      <c r="O44">
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1304</v>
       </c>
@@ -8880,22 +9886,31 @@
         <v>1648</v>
       </c>
       <c r="H45" t="s">
+        <v>1645</v>
+      </c>
+      <c r="I45" t="s">
+        <v>2377</v>
+      </c>
+      <c r="J45" t="s">
+        <v>2378</v>
+      </c>
+      <c r="K45" t="s">
         <v>1257</v>
       </c>
-      <c r="I45" t="s">
+      <c r="L45" t="s">
         <v>1260</v>
       </c>
-      <c r="J45" t="s">
+      <c r="M45" t="s">
         <v>1306</v>
       </c>
-      <c r="K45" t="s">
+      <c r="N45" t="s">
         <v>13</v>
       </c>
-      <c r="L45">
+      <c r="O45">
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1307</v>
       </c>
@@ -8918,22 +9933,31 @@
         <v>1652</v>
       </c>
       <c r="H46" t="s">
+        <v>1649</v>
+      </c>
+      <c r="I46" t="s">
+        <v>2379</v>
+      </c>
+      <c r="J46" t="s">
+        <v>2380</v>
+      </c>
+      <c r="K46" t="s">
         <v>1257</v>
       </c>
-      <c r="I46" t="s">
+      <c r="L46" t="s">
         <v>1260</v>
       </c>
-      <c r="J46" t="s">
+      <c r="M46" t="s">
         <v>1309</v>
       </c>
-      <c r="K46" t="s">
+      <c r="N46" t="s">
         <v>13</v>
       </c>
-      <c r="L46">
+      <c r="O46">
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>1328</v>
       </c>
@@ -8956,22 +9980,31 @@
         <v>1679</v>
       </c>
       <c r="H47" t="s">
+        <v>1676</v>
+      </c>
+      <c r="I47" t="s">
+        <v>2381</v>
+      </c>
+      <c r="J47" t="s">
+        <v>2382</v>
+      </c>
+      <c r="K47" t="s">
         <v>1257</v>
       </c>
-      <c r="I47" t="s">
+      <c r="L47" t="s">
         <v>1260</v>
       </c>
-      <c r="J47" t="s">
+      <c r="M47" t="s">
         <v>1330</v>
       </c>
-      <c r="K47" t="s">
+      <c r="N47" t="s">
         <v>13</v>
       </c>
-      <c r="L47">
+      <c r="O47">
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>1331</v>
       </c>
@@ -8994,22 +10027,31 @@
         <v>1683</v>
       </c>
       <c r="H48" t="s">
+        <v>1680</v>
+      </c>
+      <c r="I48" t="s">
+        <v>2383</v>
+      </c>
+      <c r="J48" t="s">
+        <v>2384</v>
+      </c>
+      <c r="K48" t="s">
         <v>1257</v>
       </c>
-      <c r="I48" t="s">
+      <c r="L48" t="s">
         <v>1260</v>
       </c>
-      <c r="J48" t="s">
+      <c r="M48" t="s">
         <v>1310</v>
       </c>
-      <c r="K48" t="s">
+      <c r="N48" t="s">
         <v>13</v>
       </c>
-      <c r="L48">
+      <c r="O48">
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>1333</v>
       </c>
@@ -9032,22 +10074,31 @@
         <v>1687</v>
       </c>
       <c r="H49" t="s">
+        <v>1684</v>
+      </c>
+      <c r="I49" t="s">
+        <v>2385</v>
+      </c>
+      <c r="J49" t="s">
+        <v>2386</v>
+      </c>
+      <c r="K49" t="s">
         <v>1257</v>
       </c>
-      <c r="I49" t="s">
+      <c r="L49" t="s">
         <v>1260</v>
       </c>
-      <c r="J49" t="s">
+      <c r="M49" t="s">
         <v>1335</v>
       </c>
-      <c r="K49" t="s">
+      <c r="N49" t="s">
         <v>13</v>
       </c>
-      <c r="L49">
+      <c r="O49">
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>1336</v>
       </c>
@@ -9070,22 +10121,31 @@
         <v>1691</v>
       </c>
       <c r="H50" t="s">
+        <v>1688</v>
+      </c>
+      <c r="I50" t="s">
+        <v>2387</v>
+      </c>
+      <c r="J50" t="s">
+        <v>2388</v>
+      </c>
+      <c r="K50" t="s">
         <v>1257</v>
       </c>
-      <c r="I50" t="s">
+      <c r="L50" t="s">
         <v>1260</v>
       </c>
-      <c r="J50" t="s">
+      <c r="M50" t="s">
         <v>1338</v>
       </c>
-      <c r="K50" t="s">
+      <c r="N50" t="s">
         <v>13</v>
       </c>
-      <c r="L50">
+      <c r="O50">
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>1339</v>
       </c>
@@ -9108,22 +10168,31 @@
         <v>1695</v>
       </c>
       <c r="H51" t="s">
+        <v>1692</v>
+      </c>
+      <c r="I51" t="s">
+        <v>2389</v>
+      </c>
+      <c r="J51" t="s">
+        <v>2390</v>
+      </c>
+      <c r="K51" t="s">
         <v>1257</v>
       </c>
-      <c r="I51" t="s">
+      <c r="L51" t="s">
         <v>1260</v>
       </c>
-      <c r="J51" t="s">
+      <c r="M51" t="s">
         <v>1341</v>
       </c>
-      <c r="K51" t="s">
+      <c r="N51" t="s">
         <v>13</v>
       </c>
-      <c r="L51">
+      <c r="O51">
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>1342</v>
       </c>
@@ -9146,22 +10215,31 @@
         <v>1471</v>
       </c>
       <c r="H52" t="s">
+        <v>1634</v>
+      </c>
+      <c r="I52" t="s">
+        <v>2373</v>
+      </c>
+      <c r="J52" t="s">
+        <v>2374</v>
+      </c>
+      <c r="K52" t="s">
         <v>1257</v>
       </c>
-      <c r="I52" t="s">
+      <c r="L52" t="s">
         <v>1260</v>
       </c>
-      <c r="J52" t="s">
+      <c r="M52" t="s">
         <v>1298</v>
       </c>
-      <c r="K52" t="s">
+      <c r="N52" t="s">
         <v>13</v>
       </c>
-      <c r="L52">
+      <c r="O52">
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>1270</v>
       </c>
@@ -9183,17 +10261,26 @@
       <c r="G53" t="s">
         <v>1601</v>
       </c>
+      <c r="H53" t="s">
+        <v>1598</v>
+      </c>
       <c r="I53" t="s">
+        <v>2365</v>
+      </c>
+      <c r="J53" t="s">
+        <v>2366</v>
+      </c>
+      <c r="L53" t="s">
         <v>1260</v>
       </c>
-      <c r="J53" t="s">
+      <c r="M53" t="s">
         <v>1349</v>
       </c>
-      <c r="L53">
+      <c r="O53">
         <v>16</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>1352</v>
       </c>
@@ -9215,17 +10302,26 @@
       <c r="G54" t="s">
         <v>1710</v>
       </c>
+      <c r="H54" t="s">
+        <v>1707</v>
+      </c>
       <c r="I54" t="s">
+        <v>2391</v>
+      </c>
+      <c r="J54" t="s">
+        <v>2392</v>
+      </c>
+      <c r="L54" t="s">
         <v>1260</v>
       </c>
-      <c r="J54" t="s">
+      <c r="M54" t="s">
         <v>1354</v>
       </c>
-      <c r="L54">
+      <c r="O54">
         <v>16</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>1359</v>
       </c>
@@ -9247,17 +10343,26 @@
       <c r="G55" t="s">
         <v>1717</v>
       </c>
+      <c r="H55" t="s">
+        <v>1714</v>
+      </c>
       <c r="I55" t="s">
+        <v>2393</v>
+      </c>
+      <c r="J55" t="s">
+        <v>2394</v>
+      </c>
+      <c r="L55" t="s">
         <v>1260</v>
       </c>
-      <c r="J55" t="s">
+      <c r="M55" t="s">
         <v>1360</v>
       </c>
-      <c r="L55">
+      <c r="O55">
         <v>16</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>1361</v>
       </c>
@@ -9279,17 +10384,26 @@
       <c r="G56" t="s">
         <v>1721</v>
       </c>
+      <c r="H56" t="s">
+        <v>1718</v>
+      </c>
       <c r="I56" t="s">
+        <v>2395</v>
+      </c>
+      <c r="J56" t="s">
+        <v>2396</v>
+      </c>
+      <c r="L56" t="s">
         <v>1260</v>
       </c>
-      <c r="J56" t="s">
+      <c r="M56" t="s">
         <v>1363</v>
       </c>
-      <c r="L56">
+      <c r="O56">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>1369</v>
       </c>
@@ -9311,17 +10425,26 @@
       <c r="G57" t="s">
         <v>1625</v>
       </c>
+      <c r="H57" t="s">
+        <v>1622</v>
+      </c>
       <c r="I57" t="s">
+        <v>2371</v>
+      </c>
+      <c r="J57" t="s">
+        <v>2372</v>
+      </c>
+      <c r="L57" t="s">
         <v>1260</v>
       </c>
-      <c r="J57" t="s">
+      <c r="M57" t="s">
         <v>1370</v>
       </c>
-      <c r="L57">
+      <c r="O57">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>1371</v>
       </c>
@@ -9343,17 +10466,26 @@
       <c r="G58" t="s">
         <v>1729</v>
       </c>
+      <c r="H58" t="s">
+        <v>1726</v>
+      </c>
       <c r="I58" t="s">
+        <v>2397</v>
+      </c>
+      <c r="J58" t="s">
+        <v>2398</v>
+      </c>
+      <c r="L58" t="s">
         <v>1260</v>
       </c>
-      <c r="J58" t="s">
+      <c r="M58" t="s">
         <v>1373</v>
       </c>
-      <c r="L58">
+      <c r="O58">
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>1374</v>
       </c>
@@ -9375,17 +10507,26 @@
       <c r="G59" t="s">
         <v>1733</v>
       </c>
+      <c r="H59" t="s">
+        <v>1730</v>
+      </c>
       <c r="I59" t="s">
+        <v>2399</v>
+      </c>
+      <c r="J59" t="s">
+        <v>2400</v>
+      </c>
+      <c r="L59" t="s">
         <v>1260</v>
       </c>
-      <c r="J59" t="s">
+      <c r="M59" t="s">
         <v>1376</v>
       </c>
-      <c r="L59">
+      <c r="O59">
         <v>16</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>1380</v>
       </c>
@@ -9407,17 +10548,26 @@
       <c r="G60" t="s">
         <v>1741</v>
       </c>
+      <c r="H60" t="s">
+        <v>1738</v>
+      </c>
       <c r="I60" t="s">
+        <v>2401</v>
+      </c>
+      <c r="J60" t="s">
+        <v>2402</v>
+      </c>
+      <c r="L60" t="s">
         <v>1260</v>
       </c>
-      <c r="J60" t="s">
+      <c r="M60" t="s">
         <v>1382</v>
       </c>
-      <c r="L60">
+      <c r="O60">
         <v>16</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>1383</v>
       </c>
@@ -9439,17 +10589,26 @@
       <c r="G61" t="s">
         <v>1745</v>
       </c>
+      <c r="H61" t="s">
+        <v>1742</v>
+      </c>
       <c r="I61" t="s">
+        <v>2403</v>
+      </c>
+      <c r="J61" t="s">
+        <v>2404</v>
+      </c>
+      <c r="L61" t="s">
         <v>1260</v>
       </c>
-      <c r="J61" t="s">
+      <c r="M61" t="s">
         <v>1385</v>
       </c>
-      <c r="L61">
+      <c r="O61">
         <v>16</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>1386</v>
       </c>
@@ -9471,17 +10630,26 @@
       <c r="G62" t="s">
         <v>1633</v>
       </c>
+      <c r="H62" t="s">
+        <v>1630</v>
+      </c>
       <c r="I62" t="s">
+        <v>2405</v>
+      </c>
+      <c r="J62" t="s">
+        <v>2406</v>
+      </c>
+      <c r="L62" t="s">
         <v>1260</v>
       </c>
-      <c r="J62" t="s">
+      <c r="M62" t="s">
         <v>1387</v>
       </c>
-      <c r="L62">
+      <c r="O62">
         <v>16</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>1388</v>
       </c>
@@ -9503,17 +10671,26 @@
       <c r="G63" t="s">
         <v>1749</v>
       </c>
+      <c r="H63" t="s">
+        <v>1746</v>
+      </c>
       <c r="I63" t="s">
+        <v>2407</v>
+      </c>
+      <c r="J63" t="s">
+        <v>2408</v>
+      </c>
+      <c r="L63" t="s">
         <v>1260</v>
       </c>
-      <c r="J63" t="s">
+      <c r="M63" t="s">
         <v>1390</v>
       </c>
-      <c r="L63">
+      <c r="O63">
         <v>16</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>1391</v>
       </c>
@@ -9535,17 +10712,26 @@
       <c r="G64" t="s">
         <v>1753</v>
       </c>
+      <c r="H64" t="s">
+        <v>1750</v>
+      </c>
       <c r="I64" t="s">
+        <v>2409</v>
+      </c>
+      <c r="J64" t="s">
+        <v>2410</v>
+      </c>
+      <c r="L64" t="s">
         <v>1260</v>
       </c>
-      <c r="J64" t="s">
+      <c r="M64" t="s">
         <v>1327</v>
       </c>
-      <c r="L64">
+      <c r="O64">
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>1399</v>
       </c>
@@ -9567,17 +10753,26 @@
       <c r="G65" t="s">
         <v>1777</v>
       </c>
+      <c r="H65" t="s">
+        <v>1774</v>
+      </c>
       <c r="I65" t="s">
+        <v>2411</v>
+      </c>
+      <c r="J65" t="s">
+        <v>2412</v>
+      </c>
+      <c r="L65" t="s">
         <v>1260</v>
       </c>
-      <c r="J65" t="s">
+      <c r="M65" t="s">
         <v>1401</v>
       </c>
-      <c r="L65">
+      <c r="O65">
         <v>16</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>1402</v>
       </c>
@@ -9599,17 +10794,26 @@
       <c r="G66" t="s">
         <v>1781</v>
       </c>
+      <c r="H66" t="s">
+        <v>1778</v>
+      </c>
       <c r="I66" t="s">
+        <v>2413</v>
+      </c>
+      <c r="J66" t="s">
+        <v>2414</v>
+      </c>
+      <c r="L66" t="s">
         <v>1260</v>
       </c>
-      <c r="J66" t="s">
+      <c r="M66" t="s">
         <v>1404</v>
       </c>
-      <c r="L66">
+      <c r="O66">
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>1405</v>
       </c>
@@ -9631,17 +10835,26 @@
       <c r="G67" t="s">
         <v>1785</v>
       </c>
+      <c r="H67" t="s">
+        <v>1782</v>
+      </c>
       <c r="I67" t="s">
+        <v>2415</v>
+      </c>
+      <c r="J67" t="s">
+        <v>2416</v>
+      </c>
+      <c r="L67" t="s">
         <v>1260</v>
       </c>
-      <c r="J67" t="s">
+      <c r="M67" t="s">
         <v>1407</v>
       </c>
-      <c r="L67">
+      <c r="O67">
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>1408</v>
       </c>
@@ -9663,17 +10876,26 @@
       <c r="G68" t="s">
         <v>1789</v>
       </c>
+      <c r="H68" t="s">
+        <v>1786</v>
+      </c>
       <c r="I68" t="s">
+        <v>2417</v>
+      </c>
+      <c r="J68" t="s">
+        <v>2418</v>
+      </c>
+      <c r="L68" t="s">
         <v>1260</v>
       </c>
-      <c r="J68" t="s">
+      <c r="M68" t="s">
         <v>1410</v>
       </c>
-      <c r="L68">
+      <c r="O68">
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>1414</v>
       </c>
@@ -9695,17 +10917,26 @@
       <c r="G69" t="s">
         <v>1797</v>
       </c>
+      <c r="H69" t="s">
+        <v>1794</v>
+      </c>
       <c r="I69" t="s">
+        <v>2419</v>
+      </c>
+      <c r="J69" t="s">
+        <v>2420</v>
+      </c>
+      <c r="L69" t="s">
         <v>1260</v>
       </c>
-      <c r="J69" t="s">
+      <c r="M69" t="s">
         <v>1415</v>
       </c>
-      <c r="L69">
+      <c r="O69">
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>1416</v>
       </c>
@@ -9727,17 +10958,26 @@
       <c r="G70" t="s">
         <v>1801</v>
       </c>
+      <c r="H70" t="s">
+        <v>1798</v>
+      </c>
       <c r="I70" t="s">
+        <v>2421</v>
+      </c>
+      <c r="J70" t="s">
+        <v>2422</v>
+      </c>
+      <c r="L70" t="s">
         <v>1260</v>
       </c>
-      <c r="J70" t="s">
+      <c r="M70" t="s">
         <v>1418</v>
       </c>
-      <c r="L70">
+      <c r="O70">
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>1419</v>
       </c>
@@ -9759,17 +10999,26 @@
       <c r="G71" t="s">
         <v>1805</v>
       </c>
+      <c r="H71" t="s">
+        <v>1802</v>
+      </c>
       <c r="I71" t="s">
+        <v>2423</v>
+      </c>
+      <c r="J71" t="s">
+        <v>2424</v>
+      </c>
+      <c r="L71" t="s">
         <v>1260</v>
       </c>
-      <c r="J71" t="s">
+      <c r="M71" t="s">
         <v>1421</v>
       </c>
-      <c r="L71">
+      <c r="O71">
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>1425</v>
       </c>
@@ -9791,17 +11040,26 @@
       <c r="G72" t="s">
         <v>1813</v>
       </c>
+      <c r="H72" t="s">
+        <v>1810</v>
+      </c>
       <c r="I72" t="s">
+        <v>2425</v>
+      </c>
+      <c r="J72" t="s">
+        <v>2426</v>
+      </c>
+      <c r="L72" t="s">
         <v>1260</v>
       </c>
-      <c r="J72" t="s">
+      <c r="M72" t="s">
         <v>1427</v>
       </c>
-      <c r="L72">
+      <c r="O72">
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>1428</v>
       </c>
@@ -9823,17 +11081,26 @@
       <c r="G73" t="s">
         <v>1817</v>
       </c>
+      <c r="H73" t="s">
+        <v>1814</v>
+      </c>
       <c r="I73" t="s">
+        <v>2427</v>
+      </c>
+      <c r="J73" t="s">
+        <v>2428</v>
+      </c>
+      <c r="L73" t="s">
         <v>1260</v>
       </c>
-      <c r="J73" t="s">
+      <c r="M73" t="s">
         <v>1430</v>
       </c>
-      <c r="L73">
+      <c r="O73">
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>1431</v>
       </c>
@@ -9855,17 +11122,26 @@
       <c r="G74" t="s">
         <v>1821</v>
       </c>
+      <c r="H74" t="s">
+        <v>1818</v>
+      </c>
       <c r="I74" t="s">
+        <v>2429</v>
+      </c>
+      <c r="J74" t="s">
+        <v>2430</v>
+      </c>
+      <c r="L74" t="s">
         <v>1260</v>
       </c>
-      <c r="J74" t="s">
+      <c r="M74" t="s">
         <v>1433</v>
       </c>
-      <c r="L74">
+      <c r="O74">
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>1435</v>
       </c>
@@ -9887,17 +11163,26 @@
       <c r="G75" t="s">
         <v>1825</v>
       </c>
+      <c r="H75" t="s">
+        <v>1822</v>
+      </c>
       <c r="I75" t="s">
+        <v>2431</v>
+      </c>
+      <c r="J75" t="s">
+        <v>2432</v>
+      </c>
+      <c r="L75" t="s">
         <v>1260</v>
       </c>
-      <c r="J75" t="s">
+      <c r="M75" t="s">
         <v>1437</v>
       </c>
-      <c r="L75">
+      <c r="O75">
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>1438</v>
       </c>
@@ -9919,17 +11204,26 @@
       <c r="G76" t="s">
         <v>1829</v>
       </c>
+      <c r="H76" t="s">
+        <v>1826</v>
+      </c>
       <c r="I76" t="s">
+        <v>2433</v>
+      </c>
+      <c r="J76" t="s">
+        <v>2434</v>
+      </c>
+      <c r="L76" t="s">
         <v>1260</v>
       </c>
-      <c r="J76" t="s">
+      <c r="M76" t="s">
         <v>1440</v>
       </c>
-      <c r="L76">
+      <c r="O76">
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>1441</v>
       </c>
@@ -9951,17 +11245,26 @@
       <c r="G77" t="s">
         <v>1833</v>
       </c>
+      <c r="H77" t="s">
+        <v>1830</v>
+      </c>
       <c r="I77" t="s">
+        <v>2435</v>
+      </c>
+      <c r="J77" t="s">
+        <v>2436</v>
+      </c>
+      <c r="L77" t="s">
         <v>1260</v>
       </c>
-      <c r="J77" t="s">
+      <c r="M77" t="s">
         <v>1443</v>
       </c>
-      <c r="L77">
+      <c r="O77">
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>1444</v>
       </c>
@@ -9983,17 +11286,26 @@
       <c r="G78" t="s">
         <v>1837</v>
       </c>
+      <c r="H78" t="s">
+        <v>1834</v>
+      </c>
       <c r="I78" t="s">
+        <v>2437</v>
+      </c>
+      <c r="J78" t="s">
+        <v>2438</v>
+      </c>
+      <c r="L78" t="s">
         <v>1260</v>
       </c>
-      <c r="J78" t="s">
+      <c r="M78" t="s">
         <v>1446</v>
       </c>
-      <c r="L78">
+      <c r="O78">
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>1447</v>
       </c>
@@ -10015,17 +11327,26 @@
       <c r="G79" t="s">
         <v>1841</v>
       </c>
+      <c r="H79" t="s">
+        <v>1838</v>
+      </c>
       <c r="I79" t="s">
+        <v>2439</v>
+      </c>
+      <c r="J79" t="s">
+        <v>2440</v>
+      </c>
+      <c r="L79" t="s">
         <v>1260</v>
       </c>
-      <c r="J79" t="s">
+      <c r="M79" t="s">
         <v>1449</v>
       </c>
-      <c r="L79">
+      <c r="O79">
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>1328</v>
       </c>
@@ -10047,17 +11368,26 @@
       <c r="G80" t="s">
         <v>1679</v>
       </c>
+      <c r="H80" t="s">
+        <v>1676</v>
+      </c>
       <c r="I80" t="s">
+        <v>2381</v>
+      </c>
+      <c r="J80" t="s">
+        <v>2382</v>
+      </c>
+      <c r="L80" t="s">
         <v>1260</v>
       </c>
-      <c r="J80" t="s">
+      <c r="M80" t="s">
         <v>1330</v>
       </c>
-      <c r="L80">
+      <c r="O80">
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>1331</v>
       </c>
@@ -10079,17 +11409,26 @@
       <c r="G81" t="s">
         <v>1683</v>
       </c>
+      <c r="H81" t="s">
+        <v>1680</v>
+      </c>
       <c r="I81" t="s">
+        <v>2383</v>
+      </c>
+      <c r="J81" t="s">
+        <v>2384</v>
+      </c>
+      <c r="L81" t="s">
         <v>1260</v>
       </c>
-      <c r="J81" t="s">
+      <c r="M81" t="s">
         <v>1450</v>
       </c>
-      <c r="L81">
+      <c r="O81">
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>1270</v>
       </c>
@@ -10111,17 +11450,26 @@
       <c r="G82" t="s">
         <v>1601</v>
       </c>
+      <c r="H82" t="s">
+        <v>1598</v>
+      </c>
       <c r="I82" t="s">
+        <v>2365</v>
+      </c>
+      <c r="J82" t="s">
+        <v>2366</v>
+      </c>
+      <c r="L82" t="s">
         <v>1260</v>
       </c>
-      <c r="J82" t="s">
+      <c r="M82" t="s">
         <v>1451</v>
       </c>
-      <c r="L82">
+      <c r="O82">
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>1452</v>
       </c>
@@ -10143,17 +11491,26 @@
       <c r="G83" t="s">
         <v>1687</v>
       </c>
+      <c r="H83" t="s">
+        <v>1684</v>
+      </c>
       <c r="I83" t="s">
+        <v>2385</v>
+      </c>
+      <c r="J83" t="s">
+        <v>2386</v>
+      </c>
+      <c r="L83" t="s">
         <v>1260</v>
       </c>
-      <c r="J83" t="s">
+      <c r="M83" t="s">
         <v>1453</v>
       </c>
-      <c r="L83">
+      <c r="O83">
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>1336</v>
       </c>
@@ -10175,17 +11532,26 @@
       <c r="G84" t="s">
         <v>1691</v>
       </c>
+      <c r="H84" t="s">
+        <v>1688</v>
+      </c>
       <c r="I84" t="s">
+        <v>2387</v>
+      </c>
+      <c r="J84" t="s">
+        <v>2388</v>
+      </c>
+      <c r="L84" t="s">
         <v>1260</v>
       </c>
-      <c r="J84" t="s">
+      <c r="M84" t="s">
         <v>1338</v>
       </c>
-      <c r="L84">
+      <c r="O84">
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>1339</v>
       </c>
@@ -10207,17 +11573,26 @@
       <c r="G85" t="s">
         <v>1695</v>
       </c>
+      <c r="H85" t="s">
+        <v>1692</v>
+      </c>
       <c r="I85" t="s">
+        <v>2389</v>
+      </c>
+      <c r="J85" t="s">
+        <v>2390</v>
+      </c>
+      <c r="L85" t="s">
         <v>1260</v>
       </c>
-      <c r="J85" t="s">
+      <c r="M85" t="s">
         <v>1341</v>
       </c>
-      <c r="L85">
+      <c r="O85">
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>1455</v>
       </c>
@@ -10239,17 +11614,26 @@
       <c r="G86" t="s">
         <v>1471</v>
       </c>
+      <c r="H86" t="s">
+        <v>1634</v>
+      </c>
       <c r="I86" t="s">
+        <v>2373</v>
+      </c>
+      <c r="J86" t="s">
+        <v>2374</v>
+      </c>
+      <c r="L86" t="s">
         <v>1260</v>
       </c>
-      <c r="J86" t="s">
+      <c r="M86" t="s">
         <v>1456</v>
       </c>
-      <c r="L86">
+      <c r="O86">
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>1272</v>
       </c>
@@ -10271,17 +11655,26 @@
       <c r="G87" t="s">
         <v>1605</v>
       </c>
+      <c r="H87" t="s">
+        <v>1602</v>
+      </c>
       <c r="I87" t="s">
+        <v>2367</v>
+      </c>
+      <c r="J87" t="s">
+        <v>2368</v>
+      </c>
+      <c r="L87" t="s">
         <v>1260</v>
       </c>
-      <c r="J87" t="s">
+      <c r="M87" t="s">
         <v>1458</v>
       </c>
-      <c r="L87">
+      <c r="O87">
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>1459</v>
       </c>
@@ -10303,17 +11696,26 @@
       <c r="G88" t="s">
         <v>1757</v>
       </c>
+      <c r="H88" t="s">
+        <v>1754</v>
+      </c>
       <c r="I88" t="s">
+        <v>2441</v>
+      </c>
+      <c r="J88" t="s">
+        <v>2442</v>
+      </c>
+      <c r="L88" t="s">
         <v>1260</v>
       </c>
-      <c r="J88" t="s">
+      <c r="M88" t="s">
         <v>1461</v>
       </c>
-      <c r="L88">
+      <c r="O88">
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>1468</v>
       </c>
@@ -10335,17 +11737,26 @@
       <c r="G89" t="s">
         <v>1849</v>
       </c>
+      <c r="H89" t="s">
+        <v>1846</v>
+      </c>
       <c r="I89" t="s">
+        <v>2443</v>
+      </c>
+      <c r="J89" t="s">
+        <v>2444</v>
+      </c>
+      <c r="L89" t="s">
         <v>1260</v>
       </c>
-      <c r="J89" t="s">
+      <c r="M89" t="s">
         <v>1470</v>
       </c>
-      <c r="L89">
+      <c r="O89">
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>1473</v>
       </c>
@@ -10367,17 +11778,26 @@
       <c r="G90" t="s">
         <v>1853</v>
       </c>
+      <c r="H90" t="s">
+        <v>1850</v>
+      </c>
       <c r="I90" t="s">
+        <v>2445</v>
+      </c>
+      <c r="J90" t="s">
+        <v>2446</v>
+      </c>
+      <c r="L90" t="s">
         <v>1260</v>
       </c>
-      <c r="J90" t="s">
+      <c r="M90" t="s">
         <v>1475</v>
       </c>
-      <c r="L90">
+      <c r="O90">
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>1482</v>
       </c>
@@ -10399,17 +11819,26 @@
       <c r="G91" t="s">
         <v>1865</v>
       </c>
+      <c r="H91" t="s">
+        <v>1862</v>
+      </c>
       <c r="I91" t="s">
+        <v>2447</v>
+      </c>
+      <c r="J91" t="s">
+        <v>2448</v>
+      </c>
+      <c r="L91" t="s">
         <v>1260</v>
       </c>
-      <c r="J91" t="s">
+      <c r="M91" t="s">
         <v>1484</v>
       </c>
-      <c r="L91">
+      <c r="O91">
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>1485</v>
       </c>
@@ -10431,17 +11860,26 @@
       <c r="G92" t="s">
         <v>1869</v>
       </c>
+      <c r="H92" t="s">
+        <v>1866</v>
+      </c>
       <c r="I92" t="s">
+        <v>2449</v>
+      </c>
+      <c r="J92" t="s">
+        <v>2450</v>
+      </c>
+      <c r="L92" t="s">
         <v>1260</v>
       </c>
-      <c r="J92" t="s">
+      <c r="M92" t="s">
         <v>1487</v>
       </c>
-      <c r="L92">
+      <c r="O92">
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>1491</v>
       </c>
@@ -10463,17 +11901,26 @@
       <c r="G93" t="s">
         <v>1877</v>
       </c>
+      <c r="H93" t="s">
+        <v>1874</v>
+      </c>
       <c r="I93" t="s">
+        <v>2451</v>
+      </c>
+      <c r="J93" t="s">
+        <v>2452</v>
+      </c>
+      <c r="L93" t="s">
         <v>1260</v>
       </c>
-      <c r="J93" t="s">
+      <c r="M93" t="s">
         <v>1493</v>
       </c>
-      <c r="L93">
+      <c r="O93">
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>1494</v>
       </c>
@@ -10495,17 +11942,26 @@
       <c r="G94" t="s">
         <v>1881</v>
       </c>
+      <c r="H94" t="s">
+        <v>1878</v>
+      </c>
       <c r="I94" t="s">
+        <v>2453</v>
+      </c>
+      <c r="J94" t="s">
+        <v>2454</v>
+      </c>
+      <c r="L94" t="s">
         <v>1260</v>
       </c>
-      <c r="J94" t="s">
+      <c r="M94" t="s">
         <v>1496</v>
       </c>
-      <c r="L94">
+      <c r="O94">
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>1497</v>
       </c>
@@ -10527,17 +11983,26 @@
       <c r="G95" t="s">
         <v>1885</v>
       </c>
+      <c r="H95" t="s">
+        <v>1882</v>
+      </c>
       <c r="I95" t="s">
+        <v>2455</v>
+      </c>
+      <c r="J95" t="s">
+        <v>2456</v>
+      </c>
+      <c r="L95" t="s">
         <v>1260</v>
       </c>
-      <c r="J95" t="s">
+      <c r="M95" t="s">
         <v>1499</v>
       </c>
-      <c r="L95">
+      <c r="O95">
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>1500</v>
       </c>
@@ -10559,17 +12024,26 @@
       <c r="G96" t="s">
         <v>1889</v>
       </c>
+      <c r="H96" t="s">
+        <v>1886</v>
+      </c>
       <c r="I96" t="s">
+        <v>2457</v>
+      </c>
+      <c r="J96" t="s">
+        <v>2458</v>
+      </c>
+      <c r="L96" t="s">
         <v>1260</v>
       </c>
-      <c r="J96" t="s">
+      <c r="M96" t="s">
         <v>1502</v>
       </c>
-      <c r="L96">
+      <c r="O96">
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>1503</v>
       </c>
@@ -10591,17 +12065,26 @@
       <c r="G97" t="s">
         <v>1893</v>
       </c>
+      <c r="H97" t="s">
+        <v>1890</v>
+      </c>
       <c r="I97" t="s">
+        <v>2459</v>
+      </c>
+      <c r="J97" t="s">
+        <v>2460</v>
+      </c>
+      <c r="L97" t="s">
         <v>1260</v>
       </c>
-      <c r="J97" t="s">
+      <c r="M97" t="s">
         <v>1505</v>
       </c>
-      <c r="L97">
+      <c r="O97">
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>1506</v>
       </c>
@@ -10623,17 +12106,26 @@
       <c r="G98" t="s">
         <v>1897</v>
       </c>
+      <c r="H98" t="s">
+        <v>1894</v>
+      </c>
       <c r="I98" t="s">
+        <v>2461</v>
+      </c>
+      <c r="J98" t="s">
+        <v>2462</v>
+      </c>
+      <c r="L98" t="s">
         <v>1260</v>
       </c>
-      <c r="J98" t="s">
+      <c r="M98" t="s">
         <v>1508</v>
       </c>
-      <c r="L98">
+      <c r="O98">
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>1509</v>
       </c>
@@ -10655,17 +12147,26 @@
       <c r="G99" t="s">
         <v>1901</v>
       </c>
+      <c r="H99" t="s">
+        <v>1898</v>
+      </c>
       <c r="I99" t="s">
+        <v>2463</v>
+      </c>
+      <c r="J99" t="s">
+        <v>2464</v>
+      </c>
+      <c r="L99" t="s">
         <v>1260</v>
       </c>
-      <c r="J99" t="s">
+      <c r="M99" t="s">
         <v>1511</v>
       </c>
-      <c r="L99">
+      <c r="O99">
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>1512</v>
       </c>
@@ -10687,17 +12188,26 @@
       <c r="G100" t="s">
         <v>1741</v>
       </c>
+      <c r="H100" t="s">
+        <v>1738</v>
+      </c>
       <c r="I100" t="s">
+        <v>2401</v>
+      </c>
+      <c r="J100" t="s">
+        <v>2402</v>
+      </c>
+      <c r="L100" t="s">
         <v>1260</v>
       </c>
-      <c r="J100" t="s">
+      <c r="M100" t="s">
         <v>1513</v>
       </c>
-      <c r="L100">
+      <c r="O100">
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>1514</v>
       </c>
@@ -10719,17 +12229,26 @@
       <c r="G101" t="s">
         <v>1471</v>
       </c>
+      <c r="H101" t="s">
+        <v>1634</v>
+      </c>
       <c r="I101" t="s">
+        <v>2373</v>
+      </c>
+      <c r="J101" t="s">
+        <v>2374</v>
+      </c>
+      <c r="L101" t="s">
         <v>1260</v>
       </c>
-      <c r="J101" t="s">
+      <c r="M101" t="s">
         <v>1515</v>
       </c>
-      <c r="L101">
+      <c r="O101">
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1516</v>
       </c>
@@ -10751,17 +12270,26 @@
       <c r="G102" t="s">
         <v>1905</v>
       </c>
+      <c r="H102" t="s">
+        <v>1902</v>
+      </c>
       <c r="I102" t="s">
+        <v>2465</v>
+      </c>
+      <c r="J102" t="s">
+        <v>2466</v>
+      </c>
+      <c r="L102" t="s">
         <v>1260</v>
       </c>
-      <c r="J102" t="s">
+      <c r="M102" t="s">
         <v>1518</v>
       </c>
-      <c r="L102">
+      <c r="O102">
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>1519</v>
       </c>
@@ -10783,17 +12311,26 @@
       <c r="G103" t="s">
         <v>1909</v>
       </c>
+      <c r="H103" t="s">
+        <v>1906</v>
+      </c>
       <c r="I103" t="s">
+        <v>2467</v>
+      </c>
+      <c r="J103" t="s">
+        <v>2468</v>
+      </c>
+      <c r="L103" t="s">
         <v>1260</v>
       </c>
-      <c r="J103" t="s">
+      <c r="M103" t="s">
         <v>1521</v>
       </c>
-      <c r="L103">
+      <c r="O103">
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>1525</v>
       </c>
@@ -10815,17 +12352,26 @@
       <c r="G104" t="s">
         <v>1917</v>
       </c>
+      <c r="H104" t="s">
+        <v>1914</v>
+      </c>
       <c r="I104" t="s">
+        <v>2469</v>
+      </c>
+      <c r="J104" t="s">
+        <v>2470</v>
+      </c>
+      <c r="L104" t="s">
         <v>1260</v>
       </c>
-      <c r="J104" t="s">
+      <c r="M104" t="s">
         <v>1527</v>
       </c>
-      <c r="L104">
+      <c r="O104">
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>1528</v>
       </c>
@@ -10847,17 +12393,26 @@
       <c r="G105" t="s">
         <v>1921</v>
       </c>
+      <c r="H105" t="s">
+        <v>1918</v>
+      </c>
       <c r="I105" t="s">
+        <v>2471</v>
+      </c>
+      <c r="J105" t="s">
+        <v>2472</v>
+      </c>
+      <c r="L105" t="s">
         <v>1260</v>
       </c>
-      <c r="J105" t="s">
+      <c r="M105" t="s">
         <v>1530</v>
       </c>
-      <c r="L105">
+      <c r="O105">
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>1531</v>
       </c>
@@ -10879,17 +12434,26 @@
       <c r="G106" t="s">
         <v>1925</v>
       </c>
+      <c r="H106" t="s">
+        <v>1922</v>
+      </c>
       <c r="I106" t="s">
+        <v>2473</v>
+      </c>
+      <c r="J106" t="s">
+        <v>2474</v>
+      </c>
+      <c r="L106" t="s">
         <v>1260</v>
       </c>
-      <c r="J106" t="s">
+      <c r="M106" t="s">
         <v>1533</v>
       </c>
-      <c r="L106">
+      <c r="O106">
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>1534</v>
       </c>
@@ -10911,17 +12475,26 @@
       <c r="G107" t="s">
         <v>1929</v>
       </c>
+      <c r="H107" t="s">
+        <v>1926</v>
+      </c>
       <c r="I107" t="s">
+        <v>2475</v>
+      </c>
+      <c r="J107" t="s">
+        <v>2476</v>
+      </c>
+      <c r="L107" t="s">
         <v>1260</v>
       </c>
-      <c r="J107" t="s">
+      <c r="M107" t="s">
         <v>1536</v>
       </c>
-      <c r="L107">
+      <c r="O107">
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>1540</v>
       </c>
@@ -10943,17 +12516,26 @@
       <c r="G108" t="s">
         <v>1937</v>
       </c>
+      <c r="H108" t="s">
+        <v>1934</v>
+      </c>
       <c r="I108" t="s">
+        <v>2477</v>
+      </c>
+      <c r="J108" t="s">
+        <v>2478</v>
+      </c>
+      <c r="L108" t="s">
         <v>1260</v>
       </c>
-      <c r="J108" t="s">
+      <c r="M108" t="s">
         <v>1541</v>
       </c>
-      <c r="L108">
+      <c r="O108">
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>1542</v>
       </c>
@@ -10975,17 +12557,26 @@
       <c r="G109" t="s">
         <v>1941</v>
       </c>
+      <c r="H109" t="s">
+        <v>1938</v>
+      </c>
       <c r="I109" t="s">
+        <v>2479</v>
+      </c>
+      <c r="J109" t="s">
+        <v>2480</v>
+      </c>
+      <c r="L109" t="s">
         <v>1260</v>
       </c>
-      <c r="J109" t="s">
+      <c r="M109" t="s">
         <v>1544</v>
       </c>
-      <c r="L109">
+      <c r="O109">
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>1270</v>
       </c>
@@ -11007,17 +12598,26 @@
       <c r="G110" t="s">
         <v>1601</v>
       </c>
+      <c r="H110" t="s">
+        <v>1598</v>
+      </c>
       <c r="I110" t="s">
+        <v>2365</v>
+      </c>
+      <c r="J110" t="s">
+        <v>2366</v>
+      </c>
+      <c r="L110" t="s">
         <v>1260</v>
       </c>
-      <c r="J110" t="s">
+      <c r="M110" t="s">
         <v>1553</v>
       </c>
-      <c r="L110">
+      <c r="O110">
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>1555</v>
       </c>
@@ -11039,17 +12639,26 @@
       <c r="G111" t="s">
         <v>1953</v>
       </c>
+      <c r="H111" t="s">
+        <v>1950</v>
+      </c>
       <c r="I111" t="s">
+        <v>2481</v>
+      </c>
+      <c r="J111" t="s">
+        <v>2482</v>
+      </c>
+      <c r="L111" t="s">
         <v>1260</v>
       </c>
-      <c r="J111" t="s">
+      <c r="M111" t="s">
         <v>1557</v>
       </c>
-      <c r="L111">
+      <c r="O111">
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>1558</v>
       </c>
@@ -11071,17 +12680,26 @@
       <c r="G112" t="s">
         <v>1957</v>
       </c>
+      <c r="H112" t="s">
+        <v>1954</v>
+      </c>
       <c r="I112" t="s">
+        <v>2483</v>
+      </c>
+      <c r="J112" t="s">
+        <v>2484</v>
+      </c>
+      <c r="L112" t="s">
         <v>1260</v>
       </c>
-      <c r="J112" t="s">
+      <c r="M112" t="s">
         <v>1560</v>
       </c>
-      <c r="L112">
+      <c r="O112">
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>1561</v>
       </c>
@@ -11103,17 +12721,26 @@
       <c r="G113" t="s">
         <v>1961</v>
       </c>
+      <c r="H113" t="s">
+        <v>1958</v>
+      </c>
       <c r="I113" t="s">
+        <v>2485</v>
+      </c>
+      <c r="J113" t="s">
+        <v>2486</v>
+      </c>
+      <c r="L113" t="s">
         <v>1260</v>
       </c>
-      <c r="J113" t="s">
+      <c r="M113" t="s">
         <v>1562</v>
       </c>
-      <c r="L113">
+      <c r="O113">
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>1563</v>
       </c>
@@ -11135,17 +12762,26 @@
       <c r="G114" t="s">
         <v>1965</v>
       </c>
+      <c r="H114" t="s">
+        <v>1962</v>
+      </c>
       <c r="I114" t="s">
+        <v>2487</v>
+      </c>
+      <c r="J114" t="s">
+        <v>2488</v>
+      </c>
+      <c r="L114" t="s">
         <v>1260</v>
       </c>
-      <c r="J114" t="s">
+      <c r="M114" t="s">
         <v>1565</v>
       </c>
-      <c r="L114">
+      <c r="O114">
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>1566</v>
       </c>
@@ -11167,17 +12803,26 @@
       <c r="G115" t="s">
         <v>1969</v>
       </c>
+      <c r="H115" t="s">
+        <v>1966</v>
+      </c>
       <c r="I115" t="s">
+        <v>2489</v>
+      </c>
+      <c r="J115" t="s">
+        <v>2490</v>
+      </c>
+      <c r="L115" t="s">
         <v>1260</v>
       </c>
-      <c r="J115" t="s">
+      <c r="M115" t="s">
         <v>1568</v>
       </c>
-      <c r="L115">
+      <c r="O115">
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>1491</v>
       </c>
@@ -11199,17 +12844,26 @@
       <c r="G116" t="s">
         <v>1877</v>
       </c>
+      <c r="H116" t="s">
+        <v>1874</v>
+      </c>
       <c r="I116" t="s">
+        <v>2451</v>
+      </c>
+      <c r="J116" t="s">
+        <v>2452</v>
+      </c>
+      <c r="L116" t="s">
         <v>1260</v>
       </c>
-      <c r="J116" t="s">
+      <c r="M116" t="s">
         <v>1493</v>
       </c>
-      <c r="L116">
+      <c r="O116">
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>1572</v>
       </c>
@@ -11231,17 +12885,26 @@
       <c r="G117" t="s">
         <v>1572</v>
       </c>
+      <c r="H117" t="s">
+        <v>1974</v>
+      </c>
       <c r="I117" t="s">
+        <v>2491</v>
+      </c>
+      <c r="J117" t="s">
+        <v>2492</v>
+      </c>
+      <c r="L117" t="s">
         <v>1260</v>
       </c>
-      <c r="J117" t="s">
+      <c r="M117" t="s">
         <v>1574</v>
       </c>
-      <c r="L117">
+      <c r="O117">
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>1292</v>
       </c>
@@ -11264,22 +12927,31 @@
         <v>1633</v>
       </c>
       <c r="H118" t="s">
+        <v>1630</v>
+      </c>
+      <c r="I118" t="s">
+        <v>2405</v>
+      </c>
+      <c r="J118" t="s">
+        <v>2406</v>
+      </c>
+      <c r="K118" t="s">
         <v>1257</v>
       </c>
-      <c r="I118" t="s">
+      <c r="L118" t="s">
         <v>1294</v>
       </c>
-      <c r="J118" t="s">
+      <c r="M118" t="s">
         <v>1295</v>
       </c>
-      <c r="K118" t="s">
+      <c r="N118" t="s">
         <v>13</v>
       </c>
-      <c r="L118">
+      <c r="O118">
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>1343</v>
       </c>
@@ -11302,22 +12974,31 @@
         <v>1699</v>
       </c>
       <c r="H119" t="s">
+        <v>1696</v>
+      </c>
+      <c r="I119" t="s">
+        <v>2493</v>
+      </c>
+      <c r="J119" t="s">
+        <v>2494</v>
+      </c>
+      <c r="K119" t="s">
         <v>1257</v>
       </c>
-      <c r="I119" t="s">
+      <c r="L119" t="s">
         <v>1294</v>
       </c>
-      <c r="J119" t="s">
+      <c r="M119" t="s">
         <v>1345</v>
       </c>
-      <c r="K119" t="s">
+      <c r="N119" t="s">
         <v>13</v>
       </c>
-      <c r="L119">
+      <c r="O119">
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>1411</v>
       </c>
@@ -11339,17 +13020,26 @@
       <c r="G120" t="s">
         <v>1793</v>
       </c>
+      <c r="H120" t="s">
+        <v>1790</v>
+      </c>
       <c r="I120" t="s">
+        <v>2495</v>
+      </c>
+      <c r="J120" t="s">
+        <v>2496</v>
+      </c>
+      <c r="L120" t="s">
         <v>1294</v>
       </c>
-      <c r="J120" t="s">
+      <c r="M120" t="s">
         <v>1413</v>
       </c>
-      <c r="L120">
+      <c r="O120">
         <v>16</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>1343</v>
       </c>
@@ -11371,17 +13061,26 @@
       <c r="G121" t="s">
         <v>1699</v>
       </c>
+      <c r="H121" t="s">
+        <v>1696</v>
+      </c>
       <c r="I121" t="s">
+        <v>2493</v>
+      </c>
+      <c r="J121" t="s">
+        <v>2494</v>
+      </c>
+      <c r="L121" t="s">
         <v>1294</v>
       </c>
-      <c r="J121" t="s">
+      <c r="M121" t="s">
         <v>1457</v>
       </c>
-      <c r="L121">
+      <c r="O121">
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>1488</v>
       </c>
@@ -11403,17 +13102,26 @@
       <c r="G122" t="s">
         <v>1873</v>
       </c>
+      <c r="H122" t="s">
+        <v>1870</v>
+      </c>
       <c r="I122" t="s">
+        <v>2497</v>
+      </c>
+      <c r="J122" t="s">
+        <v>2498</v>
+      </c>
+      <c r="L122" t="s">
         <v>1294</v>
       </c>
-      <c r="J122" t="s">
+      <c r="M122" t="s">
         <v>1490</v>
       </c>
-      <c r="L122">
+      <c r="O122">
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>1522</v>
       </c>
@@ -11435,19 +13143,28 @@
       <c r="G123" t="s">
         <v>1913</v>
       </c>
+      <c r="H123" t="s">
+        <v>1910</v>
+      </c>
       <c r="I123" t="s">
+        <v>2499</v>
+      </c>
+      <c r="J123" t="s">
+        <v>2500</v>
+      </c>
+      <c r="L123" t="s">
         <v>1294</v>
       </c>
-      <c r="J123" t="s">
+      <c r="M123" t="s">
         <v>1524</v>
       </c>
-      <c r="L123">
+      <c r="O123">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L123">
-    <sortCondition ref="I2:I123"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O123">
+    <sortCondition ref="L2:L123"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
